--- a/samsung/dist/20261028_三星電子個股模型_v0.3.2.xlsx
+++ b/samsung/dist/20261028_三星電子個股模型_v0.3.2.xlsx
@@ -65,9 +65,17 @@
     <definedName function="false" hidden="false" name="cqA_14" vbProcedure="false">In!$E$94</definedName>
     <definedName function="false" hidden="false" name="cqA_15" vbProcedure="false">In!$E$95</definedName>
     <definedName function="false" hidden="false" name="cqA_16" vbProcedure="false">In!$E$96</definedName>
+    <definedName function="false" hidden="false" name="cqA_16_hi" vbProcedure="false">In!$F$96</definedName>
+    <definedName function="false" hidden="false" name="cqA_16_lo" vbProcedure="false">In!$D$96</definedName>
     <definedName function="false" hidden="false" name="cqA_17" vbProcedure="false">In!$E$97</definedName>
+    <definedName function="false" hidden="false" name="cqA_17_hi" vbProcedure="false">In!$F$97</definedName>
+    <definedName function="false" hidden="false" name="cqA_17_lo" vbProcedure="false">In!$D$97</definedName>
     <definedName function="false" hidden="false" name="cqA_18" vbProcedure="false">In!$E$98</definedName>
+    <definedName function="false" hidden="false" name="cqA_18_hi" vbProcedure="false">In!$F$98</definedName>
+    <definedName function="false" hidden="false" name="cqA_18_lo" vbProcedure="false">In!$D$98</definedName>
     <definedName function="false" hidden="false" name="cqA_19" vbProcedure="false">In!$E$99</definedName>
+    <definedName function="false" hidden="false" name="cqA_19_hi" vbProcedure="false">In!$F$99</definedName>
+    <definedName function="false" hidden="false" name="cqA_19_lo" vbProcedure="false">In!$D$99</definedName>
     <definedName function="false" hidden="false" name="cqA_8" vbProcedure="false">In!$E$88</definedName>
     <definedName function="false" hidden="false" name="cqA_9" vbProcedure="false">In!$E$89</definedName>
     <definedName function="false" hidden="false" name="cqB_10" vbProcedure="false">In!$E$102</definedName>
@@ -77,9 +85,17 @@
     <definedName function="false" hidden="false" name="cqB_14" vbProcedure="false">In!$E$106</definedName>
     <definedName function="false" hidden="false" name="cqB_15" vbProcedure="false">In!$E$107</definedName>
     <definedName function="false" hidden="false" name="cqB_16" vbProcedure="false">In!$E$108</definedName>
+    <definedName function="false" hidden="false" name="cqB_16_hi" vbProcedure="false">In!$F$108</definedName>
+    <definedName function="false" hidden="false" name="cqB_16_lo" vbProcedure="false">In!$D$108</definedName>
     <definedName function="false" hidden="false" name="cqB_17" vbProcedure="false">In!$E$109</definedName>
+    <definedName function="false" hidden="false" name="cqB_17_hi" vbProcedure="false">In!$F$109</definedName>
+    <definedName function="false" hidden="false" name="cqB_17_lo" vbProcedure="false">In!$D$109</definedName>
     <definedName function="false" hidden="false" name="cqB_18" vbProcedure="false">In!$E$110</definedName>
+    <definedName function="false" hidden="false" name="cqB_18_hi" vbProcedure="false">In!$F$110</definedName>
+    <definedName function="false" hidden="false" name="cqB_18_lo" vbProcedure="false">In!$D$110</definedName>
     <definedName function="false" hidden="false" name="cqB_19" vbProcedure="false">In!$E$111</definedName>
+    <definedName function="false" hidden="false" name="cqB_19_hi" vbProcedure="false">In!$F$111</definedName>
+    <definedName function="false" hidden="false" name="cqB_19_lo" vbProcedure="false">In!$D$111</definedName>
     <definedName function="false" hidden="false" name="cqB_8" vbProcedure="false">In!$E$100</definedName>
     <definedName function="false" hidden="false" name="cqB_9" vbProcedure="false">In!$E$101</definedName>
     <definedName function="false" hidden="false" name="cqC_10" vbProcedure="false">In!$E$114</definedName>
@@ -274,9 +290,17 @@
     <definedName function="false" hidden="false" name="nqA_14" vbProcedure="false">In!$E$137</definedName>
     <definedName function="false" hidden="false" name="nqA_15" vbProcedure="false">In!$E$138</definedName>
     <definedName function="false" hidden="false" name="nqA_16" vbProcedure="false">In!$E$139</definedName>
+    <definedName function="false" hidden="false" name="nqA_16_hi" vbProcedure="false">In!$F$139</definedName>
+    <definedName function="false" hidden="false" name="nqA_16_lo" vbProcedure="false">In!$D$139</definedName>
     <definedName function="false" hidden="false" name="nqA_17" vbProcedure="false">In!$E$140</definedName>
+    <definedName function="false" hidden="false" name="nqA_17_hi" vbProcedure="false">In!$F$140</definedName>
+    <definedName function="false" hidden="false" name="nqA_17_lo" vbProcedure="false">In!$D$140</definedName>
     <definedName function="false" hidden="false" name="nqA_18" vbProcedure="false">In!$E$141</definedName>
+    <definedName function="false" hidden="false" name="nqA_18_hi" vbProcedure="false">In!$F$141</definedName>
+    <definedName function="false" hidden="false" name="nqA_18_lo" vbProcedure="false">In!$D$141</definedName>
     <definedName function="false" hidden="false" name="nqA_19" vbProcedure="false">In!$E$142</definedName>
+    <definedName function="false" hidden="false" name="nqA_19_hi" vbProcedure="false">In!$F$142</definedName>
+    <definedName function="false" hidden="false" name="nqA_19_lo" vbProcedure="false">In!$D$142</definedName>
     <definedName function="false" hidden="false" name="nqA_8" vbProcedure="false">In!$E$131</definedName>
     <definedName function="false" hidden="false" name="nqA_9" vbProcedure="false">In!$E$132</definedName>
     <definedName function="false" hidden="false" name="nqB_10" vbProcedure="false">In!$E$145</definedName>
@@ -286,9 +310,17 @@
     <definedName function="false" hidden="false" name="nqB_14" vbProcedure="false">In!$E$149</definedName>
     <definedName function="false" hidden="false" name="nqB_15" vbProcedure="false">In!$E$150</definedName>
     <definedName function="false" hidden="false" name="nqB_16" vbProcedure="false">In!$E$151</definedName>
+    <definedName function="false" hidden="false" name="nqB_16_hi" vbProcedure="false">In!$F$151</definedName>
+    <definedName function="false" hidden="false" name="nqB_16_lo" vbProcedure="false">In!$D$151</definedName>
     <definedName function="false" hidden="false" name="nqB_17" vbProcedure="false">In!$E$152</definedName>
+    <definedName function="false" hidden="false" name="nqB_17_hi" vbProcedure="false">In!$F$152</definedName>
+    <definedName function="false" hidden="false" name="nqB_17_lo" vbProcedure="false">In!$D$152</definedName>
     <definedName function="false" hidden="false" name="nqB_18" vbProcedure="false">In!$E$153</definedName>
+    <definedName function="false" hidden="false" name="nqB_18_hi" vbProcedure="false">In!$F$153</definedName>
+    <definedName function="false" hidden="false" name="nqB_18_lo" vbProcedure="false">In!$D$153</definedName>
     <definedName function="false" hidden="false" name="nqB_19" vbProcedure="false">In!$E$154</definedName>
+    <definedName function="false" hidden="false" name="nqB_19_hi" vbProcedure="false">In!$F$154</definedName>
+    <definedName function="false" hidden="false" name="nqB_19_lo" vbProcedure="false">In!$D$154</definedName>
     <definedName function="false" hidden="false" name="nqB_8" vbProcedure="false">In!$E$143</definedName>
     <definedName function="false" hidden="false" name="nqB_9" vbProcedure="false">In!$E$144</definedName>
     <definedName function="false" hidden="false" name="nqC_10" vbProcedure="false">In!$E$157</definedName>
@@ -490,7 +522,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1078">
   <si>
     <r>
       <rPr>
@@ -9224,6 +9256,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -9351,7 +9392,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">緩降</t>
+      <t xml:space="preserve">緩降（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -9923,6 +9983,103 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為本庫外推：標示來源只涵蓋到 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核）；區間＝情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同季值</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">cqA_17</t>
   </si>
   <si>
@@ -10211,6 +10368,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -10338,7 +10504,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">溫和回升</t>
+      <t xml:space="preserve">溫和回升（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -12692,6 +12877,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -12724,7 +12918,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">下半年供需平衡、價格面臨下修壓力</t>
+      <t xml:space="preserve">下半年供需平衡、價格面臨下修壓力（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -13476,6 +13689,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -13538,6 +13760,34 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">NAND $/GB 2028 −68.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -38342,66 +38592,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
         <v>4.46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
         <v>216 ／ 260</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
         <v>55 ／ 154</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
         <v>1.23255275</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
   </sheetData>
@@ -38429,111 +38679,111 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>1076</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -40326,9 +40576,9 @@
         <v>0.03</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H88" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H88" s="4" t="s">
         <v>256</v>
       </c>
     </row>
@@ -40346,7 +40596,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>211</v>
@@ -40366,7 +40616,7 @@
         <v>-0.02</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>211</v>
@@ -40386,7 +40636,7 @@
         <v>-0.03</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>211</v>
@@ -40406,7 +40656,7 @@
         <v>-0.03</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>211</v>
@@ -40426,7 +40676,7 @@
         <v>-0.03</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>211</v>
@@ -40446,7 +40696,7 @@
         <v>-0.02</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>211</v>
@@ -40466,7 +40716,7 @@
         <v>-0.02</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>211</v>
@@ -40482,31 +40732,43 @@
       <c r="C96" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D96" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E96" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F96" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G96" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>211</v>
+        <v>62</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C97" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D97" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E97" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F97" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G97" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>211</v>
@@ -40514,19 +40776,25 @@
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D98" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E98" s="7" t="n">
         <v>-0.02</v>
       </c>
+      <c r="F98" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G98" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H98" s="4" t="s">
         <v>211</v>
@@ -40534,19 +40802,25 @@
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C99" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D99" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E99" s="7" t="n">
         <v>-0.02</v>
       </c>
+      <c r="F99" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G99" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>211</v>
@@ -40554,10 +40828,10 @@
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>49</v>
@@ -40566,18 +40840,18 @@
         <v>0.05</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H100" s="8" t="s">
-        <v>281</v>
+        <v>39</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C101" s="0" t="s">
         <v>49</v>
@@ -40586,7 +40860,7 @@
         <v>0.02</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>211</v>
@@ -40594,10 +40868,10 @@
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C102" s="0" t="s">
         <v>49</v>
@@ -40606,7 +40880,7 @@
         <v>-0.08</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>211</v>
@@ -40614,10 +40888,10 @@
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C103" s="0" t="s">
         <v>49</v>
@@ -40626,7 +40900,7 @@
         <v>-0.15</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>211</v>
@@ -40634,10 +40908,10 @@
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>49</v>
@@ -40646,7 +40920,7 @@
         <v>-0.25</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>211</v>
@@ -40654,10 +40928,10 @@
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>49</v>
@@ -40666,7 +40940,7 @@
         <v>-0.15</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>211</v>
@@ -40674,10 +40948,10 @@
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>49</v>
@@ -40686,7 +40960,7 @@
         <v>-0.1</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>211</v>
@@ -40694,10 +40968,10 @@
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C107" s="0" t="s">
         <v>49</v>
@@ -40706,7 +40980,7 @@
         <v>-0.05</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>211</v>
@@ -40714,39 +40988,51 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D108" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E108" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F108" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G108" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>211</v>
+        <v>62</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D109" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E109" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F109" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G109" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>211</v>
@@ -40754,19 +41040,25 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D110" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E110" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F110" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G110" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H110" s="4" t="s">
         <v>211</v>
@@ -40774,19 +41066,25 @@
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C111" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D111" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E111" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F111" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G111" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>211</v>
@@ -40794,10 +41092,10 @@
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>49</v>
@@ -40815,15 +41113,15 @@
         <v>62</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>49</v>
@@ -40846,10 +41144,10 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>49</v>
@@ -40872,10 +41170,10 @@
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>49</v>
@@ -40898,10 +41196,10 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C116" s="0" t="s">
         <v>49</v>
@@ -40924,10 +41222,10 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C117" s="0" t="s">
         <v>49</v>
@@ -40950,10 +41248,10 @@
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C118" s="0" t="s">
         <v>49</v>
@@ -40976,10 +41274,10 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C119" s="0" t="s">
         <v>49</v>
@@ -41002,10 +41300,10 @@
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C120" s="0" t="s">
         <v>49</v>
@@ -41028,10 +41326,10 @@
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C121" s="0" t="s">
         <v>49</v>
@@ -41054,10 +41352,10 @@
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C122" s="0" t="s">
         <v>49</v>
@@ -41080,10 +41378,10 @@
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C123" s="0" t="s">
         <v>49</v>
@@ -41106,10 +41404,10 @@
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C124" s="0" t="s">
         <v>49</v>
@@ -41121,15 +41419,15 @@
         <v>66</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C125" s="0" t="s">
         <v>49</v>
@@ -41146,10 +41444,10 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C126" s="0" t="s">
         <v>49</v>
@@ -41166,10 +41464,10 @@
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C127" s="0" t="s">
         <v>49</v>
@@ -41186,10 +41484,10 @@
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C128" s="0" t="s">
         <v>49</v>
@@ -41206,10 +41504,10 @@
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C129" s="0" t="s">
         <v>49</v>
@@ -41226,10 +41524,10 @@
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C130" s="0" t="s">
         <v>49</v>
@@ -41246,10 +41544,10 @@
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>49</v>
@@ -41258,18 +41556,18 @@
         <v>0.03</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H131" s="8" t="s">
-        <v>346</v>
+        <v>39</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C132" s="0" t="s">
         <v>49</v>
@@ -41278,7 +41576,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H132" s="4" t="s">
         <v>211</v>
@@ -41286,10 +41584,10 @@
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C133" s="0" t="s">
         <v>49</v>
@@ -41298,7 +41596,7 @@
         <v>-0.05</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>211</v>
@@ -41306,10 +41604,10 @@
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C134" s="0" t="s">
         <v>49</v>
@@ -41318,7 +41616,7 @@
         <v>-0.07</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H134" s="4" t="s">
         <v>211</v>
@@ -41326,10 +41624,10 @@
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C135" s="0" t="s">
         <v>49</v>
@@ -41338,7 +41636,7 @@
         <v>-0.05</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>211</v>
@@ -41346,10 +41644,10 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C136" s="0" t="s">
         <v>49</v>
@@ -41358,7 +41656,7 @@
         <v>-0.05</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H136" s="4" t="s">
         <v>211</v>
@@ -41366,10 +41664,10 @@
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C137" s="0" t="s">
         <v>49</v>
@@ -41378,7 +41676,7 @@
         <v>-0.05</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>211</v>
@@ -41386,10 +41684,10 @@
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C138" s="0" t="s">
         <v>49</v>
@@ -41398,7 +41696,7 @@
         <v>-0.05</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>211</v>
@@ -41406,39 +41704,51 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C139" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D139" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E139" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F139" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G139" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H139" s="4" t="s">
-        <v>211</v>
+        <v>62</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C140" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D140" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E140" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F140" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G140" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H140" s="4" t="s">
         <v>211</v>
@@ -41446,19 +41756,25 @@
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C141" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D141" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E141" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F141" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G141" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>211</v>
@@ -41466,19 +41782,25 @@
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D142" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E142" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F142" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G142" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>211</v>
@@ -41486,10 +41808,10 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C143" s="0" t="s">
         <v>49</v>
@@ -41498,18 +41820,18 @@
         <v>0.05</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H143" s="8" t="s">
-        <v>371</v>
+        <v>39</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C144" s="0" t="s">
         <v>49</v>
@@ -41518,7 +41840,7 @@
         <v>0.02</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H144" s="4" t="s">
         <v>211</v>
@@ -41526,10 +41848,10 @@
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C145" s="0" t="s">
         <v>49</v>
@@ -41538,7 +41860,7 @@
         <v>-0.1</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>211</v>
@@ -41546,10 +41868,10 @@
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C146" s="0" t="s">
         <v>49</v>
@@ -41558,7 +41880,7 @@
         <v>-0.2</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H146" s="4" t="s">
         <v>211</v>
@@ -41566,10 +41888,10 @@
     </row>
     <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C147" s="0" t="s">
         <v>49</v>
@@ -41578,7 +41900,7 @@
         <v>-0.3</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>211</v>
@@ -41586,10 +41908,10 @@
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C148" s="0" t="s">
         <v>49</v>
@@ -41598,7 +41920,7 @@
         <v>-0.25</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H148" s="4" t="s">
         <v>211</v>
@@ -41606,10 +41928,10 @@
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C149" s="0" t="s">
         <v>49</v>
@@ -41618,7 +41940,7 @@
         <v>-0.2</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>211</v>
@@ -41626,10 +41948,10 @@
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C150" s="0" t="s">
         <v>49</v>
@@ -41638,7 +41960,7 @@
         <v>-0.1</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H150" s="4" t="s">
         <v>211</v>
@@ -41646,39 +41968,51 @@
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C151" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D151" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E151" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F151" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G151" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H151" s="4" t="s">
-        <v>211</v>
+        <v>62</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C152" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D152" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E152" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F152" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G152" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H152" s="4" t="s">
         <v>211</v>
@@ -41686,19 +42020,25 @@
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C153" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D153" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E153" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F153" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G153" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>211</v>
@@ -41706,19 +42046,25 @@
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C154" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D154" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E154" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F154" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G154" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>211</v>
@@ -41726,10 +42072,10 @@
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C155" s="0" t="s">
         <v>49</v>
@@ -41747,15 +42093,15 @@
         <v>62</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C156" s="0" t="s">
         <v>49</v>
@@ -41778,10 +42124,10 @@
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C157" s="0" t="s">
         <v>49</v>
@@ -41804,10 +42150,10 @@
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C158" s="0" t="s">
         <v>49</v>
@@ -41830,10 +42176,10 @@
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C159" s="0" t="s">
         <v>49</v>
@@ -41856,10 +42202,10 @@
     </row>
     <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C160" s="0" t="s">
         <v>49</v>
@@ -41882,10 +42228,10 @@
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C161" s="0" t="s">
         <v>49</v>
@@ -41908,10 +42254,10 @@
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C162" s="0" t="s">
         <v>49</v>
@@ -41934,10 +42280,10 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C163" s="0" t="s">
         <v>49</v>
@@ -41960,10 +42306,10 @@
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C164" s="0" t="s">
         <v>49</v>
@@ -41986,10 +42332,10 @@
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C165" s="0" t="s">
         <v>49</v>
@@ -42012,10 +42358,10 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C166" s="0" t="s">
         <v>49</v>
@@ -42038,18 +42384,18 @@
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E168" s="7" t="n">
         <v>5.4</v>
@@ -42058,18 +42404,18 @@
         <v>66</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E169" s="7" t="n">
         <v>2.4</v>
@@ -42083,13 +42429,13 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E170" s="7" t="n">
         <v>0.5</v>
@@ -42103,13 +42449,13 @@
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E171" s="7" t="n">
         <v>260</v>
@@ -42123,13 +42469,13 @@
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="B172" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="C172" s="0" t="s">
         <v>431</v>
-      </c>
-      <c r="B172" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C172" s="0" t="s">
-        <v>430</v>
       </c>
       <c r="E172" s="7" t="n">
         <v>280</v>
@@ -42143,13 +42489,13 @@
     </row>
     <row r="173" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E173" s="7" t="n">
         <v>288</v>
@@ -42163,13 +42509,13 @@
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E174" s="7" t="n">
         <v>1.7</v>
@@ -42178,18 +42524,18 @@
         <v>66</v>
       </c>
       <c r="H174" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E175" s="7" t="n">
         <v>7</v>
@@ -42203,13 +42549,13 @@
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E176" s="7" t="n">
         <v>7</v>
@@ -42223,13 +42569,13 @@
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E177" s="7" t="n">
         <v>288</v>
@@ -42243,13 +42589,13 @@
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E178" s="7" t="n">
         <v>288</v>
@@ -42263,13 +42609,13 @@
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E179" s="7" t="n">
         <v>288</v>
@@ -42283,13 +42629,13 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D180" s="7" t="n">
         <v>0</v>
@@ -42304,18 +42650,18 @@
         <v>62</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D181" s="7" t="n">
         <v>0</v>
@@ -42335,13 +42681,13 @@
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D182" s="7" t="n">
         <v>1</v>
@@ -42361,13 +42707,13 @@
     </row>
     <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E183" s="7" t="n">
         <v>1024</v>
@@ -42376,18 +42722,18 @@
         <v>66</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E184" s="7" t="n">
         <v>1024</v>
@@ -42401,13 +42747,13 @@
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E185" s="7" t="n">
         <v>1024</v>
@@ -42421,13 +42767,13 @@
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E186" s="7" t="n">
         <v>0.5</v>
@@ -42436,18 +42782,18 @@
         <v>66</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E187" s="7" t="n">
         <v>0</v>
@@ -42461,13 +42807,13 @@
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E188" s="7" t="n">
         <v>0</v>
@@ -42481,13 +42827,13 @@
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E189" s="7" t="n">
         <v>141</v>
@@ -42501,13 +42847,13 @@
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E190" s="7" t="n">
         <v>141</v>
@@ -42521,13 +42867,13 @@
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E191" s="7" t="n">
         <v>141</v>
@@ -42541,13 +42887,13 @@
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D192" s="7" t="n">
         <v>0.6</v>
@@ -42559,21 +42905,21 @@
         <v>0.9</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H192" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D193" s="7" t="n">
         <v>1.2</v>
@@ -42585,7 +42931,7 @@
         <v>1.8</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>211</v>
@@ -42593,13 +42939,13 @@
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D194" s="7" t="n">
         <v>1.5</v>
@@ -42611,7 +42957,7 @@
         <v>2.5</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H194" s="4" t="s">
         <v>211</v>
@@ -42619,13 +42965,13 @@
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D195" s="7" t="n">
         <v>288</v>
@@ -42637,7 +42983,7 @@
         <v>288</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>211</v>
@@ -42645,13 +42991,13 @@
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D196" s="7" t="n">
         <v>288</v>
@@ -42663,7 +43009,7 @@
         <v>432</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H196" s="4" t="s">
         <v>211</v>
@@ -42671,13 +43017,13 @@
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D197" s="7" t="n">
         <v>432</v>
@@ -42689,7 +43035,7 @@
         <v>432</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>211</v>
@@ -42697,13 +43043,13 @@
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E198" s="7" t="n">
         <v>3.85</v>
@@ -42712,18 +43058,18 @@
         <v>66</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E199" s="7" t="n">
         <v>5.5</v>
@@ -42737,13 +43083,13 @@
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E200" s="7" t="n">
         <v>7</v>
@@ -42757,13 +43103,13 @@
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E201" s="7" t="n">
         <v>192</v>
@@ -42777,13 +43123,13 @@
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E202" s="7" t="n">
         <v>250</v>
@@ -42797,13 +43143,13 @@
     </row>
     <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E203" s="7" t="n">
         <v>288</v>
@@ -42817,13 +43163,13 @@
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D204" s="7" t="n">
         <v>1.5</v>
@@ -42838,18 +43184,18 @@
         <v>62</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D205" s="7" t="n">
         <v>2</v>
@@ -42869,13 +43215,13 @@
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D206" s="7" t="n">
         <v>2</v>
@@ -42895,13 +43241,13 @@
     </row>
     <row r="207" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D207" s="7" t="n">
         <v>96</v>
@@ -42921,13 +43267,13 @@
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D208" s="7" t="n">
         <v>120</v>
@@ -42947,13 +43293,13 @@
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D209" s="7" t="n">
         <v>144</v>
@@ -42973,13 +43319,13 @@
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D210" s="7" t="n">
         <v>0.5</v>
@@ -42994,18 +43340,18 @@
         <v>149</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D211" s="7" t="n">
         <v>3</v>
@@ -43025,13 +43371,13 @@
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D212" s="7" t="n">
         <v>3.5</v>
@@ -43051,13 +43397,13 @@
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D213" s="7" t="n">
         <v>100</v>
@@ -43077,13 +43423,13 @@
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D214" s="7" t="n">
         <v>150</v>
@@ -43103,13 +43449,13 @@
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D215" s="7" t="n">
         <v>200</v>
@@ -43129,15 +43475,15 @@
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>223</v>
@@ -43149,15 +43495,15 @@
         <v>39</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C218" s="0" t="s">
         <v>223</v>
@@ -43174,10 +43520,10 @@
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C219" s="0" t="s">
         <v>223</v>
@@ -43200,10 +43546,10 @@
     </row>
     <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>223</v>
@@ -43226,10 +43572,10 @@
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>223</v>
@@ -43252,10 +43598,10 @@
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>223</v>
@@ -43278,18 +43624,18 @@
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D224" s="7" t="n">
         <v>34</v>
@@ -43304,15 +43650,15 @@
         <v>44</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>49</v>
@@ -43330,15 +43676,15 @@
         <v>66</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>223</v>
@@ -43356,15 +43702,15 @@
         <v>62</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>49</v>
@@ -43382,15 +43728,15 @@
         <v>66</v>
       </c>
       <c r="H227" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>49</v>
@@ -43408,18 +43754,18 @@
         <v>62</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D229" s="7" t="n">
         <v>12.5</v>
@@ -43434,15 +43780,15 @@
         <v>66</v>
       </c>
       <c r="H229" s="8" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>49</v>
@@ -43460,15 +43806,15 @@
         <v>66</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C231" s="0" t="s">
         <v>49</v>
@@ -43486,15 +43832,15 @@
         <v>66</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>49</v>
@@ -43512,15 +43858,15 @@
         <v>62</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>49</v>
@@ -43538,15 +43884,15 @@
         <v>62</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C234" s="0" t="s">
         <v>49</v>
@@ -43564,15 +43910,15 @@
         <v>62</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C235" s="0" t="s">
         <v>49</v>
@@ -43590,15 +43936,15 @@
         <v>62</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C236" s="0" t="s">
         <v>49</v>
@@ -43616,15 +43962,15 @@
         <v>62</v>
       </c>
       <c r="H236" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C237" s="0" t="s">
         <v>49</v>
@@ -43642,15 +43988,15 @@
         <v>62</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C238" s="0" t="s">
         <v>49</v>
@@ -43668,23 +44014,23 @@
         <v>62</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="6" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D240" s="7" t="n">
         <v>340</v>
@@ -43696,21 +44042,21 @@
         <v>400</v>
       </c>
       <c r="G240" s="8" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D241" s="7" t="n">
         <v>38</v>
@@ -43725,18 +44071,18 @@
         <v>39</v>
       </c>
       <c r="H241" s="8" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D242" s="7" t="n">
         <v>3.5</v>
@@ -43751,18 +44097,18 @@
         <v>39</v>
       </c>
       <c r="H242" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E243" s="7" t="n">
         <v>54.6</v>
@@ -43771,18 +44117,18 @@
         <v>66</v>
       </c>
       <c r="H243" s="8" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E244" s="7" t="n">
         <v>77.4</v>
@@ -43791,18 +44137,18 @@
         <v>66</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E245" s="7" t="n">
         <v>152.8</v>
@@ -43811,20 +44157,20 @@
         <v>66</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C247" s="9" t="s">
         <v>49</v>
@@ -43838,15 +44184,15 @@
         <v>62</v>
       </c>
       <c r="H247" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C248" s="9" t="s">
         <v>49</v>
@@ -43860,15 +44206,15 @@
         <v>62</v>
       </c>
       <c r="H248" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C249" s="9" t="s">
         <v>49</v>
@@ -43882,15 +44228,15 @@
         <v>62</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C250" s="9" t="s">
         <v>49</v>
@@ -43904,15 +44250,15 @@
         <v>62</v>
       </c>
       <c r="H250" s="9" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C251" s="9" t="s">
         <v>49</v>
@@ -43926,15 +44272,15 @@
         <v>62</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C252" s="9" t="s">
         <v>49</v>
@@ -43949,15 +44295,15 @@
         <v>39</v>
       </c>
       <c r="H252" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C253" s="9" t="s">
         <v>49</v>
@@ -43971,15 +44317,15 @@
         <v>62</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C254" s="9" t="s">
         <v>49</v>
@@ -43994,15 +44340,15 @@
         <v>39</v>
       </c>
       <c r="H254" s="9" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="9" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C255" s="9" t="s">
         <v>49</v>
@@ -44017,15 +44363,15 @@
         <v>62</v>
       </c>
       <c r="H255" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="9" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C256" s="9" t="s">
         <v>49</v>
@@ -44040,15 +44386,15 @@
         <v>62</v>
       </c>
       <c r="H256" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="9" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C257" s="9" t="s">
         <v>49</v>
@@ -44063,15 +44409,15 @@
         <v>62</v>
       </c>
       <c r="H257" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C258" s="9" t="s">
         <v>223</v>
@@ -44085,15 +44431,15 @@
         <v>62</v>
       </c>
       <c r="H258" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="9" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C259" s="9" t="s">
         <v>223</v>
@@ -44107,15 +44453,15 @@
         <v>62</v>
       </c>
       <c r="H259" s="9" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="9" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C260" s="9" t="s">
         <v>49</v>
@@ -44130,15 +44476,15 @@
         <v>39</v>
       </c>
       <c r="H260" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C261" s="9" t="s">
         <v>49</v>
@@ -44153,15 +44499,15 @@
         <v>39</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="9" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C262" s="9" t="s">
         <v>49</v>
@@ -44176,15 +44522,15 @@
         <v>39</v>
       </c>
       <c r="H262" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="9" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C263" s="9" t="s">
         <v>43</v>
@@ -44202,15 +44548,15 @@
         <v>66</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="9" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C264" s="9" t="s">
         <v>43</v>
@@ -44224,15 +44570,15 @@
         <v>66</v>
       </c>
       <c r="H264" s="9" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="9" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C265" s="9" t="s">
         <v>43</v>
@@ -44246,15 +44592,15 @@
         <v>66</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="9" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C266" s="9" t="s">
         <v>43</v>
@@ -44268,7 +44614,7 @@
         <v>66</v>
       </c>
       <c r="H266" s="9" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -44296,83 +44642,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="V3" s="13" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
@@ -44456,10 +44802,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1</v>
@@ -44543,10 +44889,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
@@ -44630,10 +44976,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
@@ -44717,10 +45063,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
@@ -44804,10 +45150,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
+        <v>692</v>
+      </c>
+      <c r="B10" s="0" t="s">
         <v>691</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>690</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
@@ -44891,50 +45237,50 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">AVERAGE(C4:F4)</f>
@@ -44975,10 +45321,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">AVERAGE(C5:F5)</f>
@@ -45019,10 +45365,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">AVERAGE(C6:F6)</f>
@@ -45063,10 +45409,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">AVERAGE(C8:F8)</f>
@@ -45107,10 +45453,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">AVERAGE(C9:F9)</f>
@@ -45151,10 +45497,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
+        <v>692</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>691</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>690</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">AVERAGE(C10:F10)</f>
@@ -45219,7 +45565,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45230,35 +45576,35 @@
         <v>29</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">u_bw_26*g_bw_26</f>
@@ -45275,10 +45621,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="B6" s="0" t="s">
         <v>707</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>706</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">u_rb_26*g_rb_26</f>
@@ -45295,10 +45641,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">u_ru_26*g_ru_26</f>
@@ -45315,10 +45661,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">u_hp_26*g_hp_26</f>
@@ -45335,10 +45681,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">u_amd_26*g_amd_26</f>
@@ -45355,10 +45701,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D10" s="16" t="n">
         <f aca="false">u_tpu_26*g_tpu_26</f>
@@ -45375,10 +45721,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">u_trn_26*g_trn_26</f>
@@ -45395,10 +45741,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">u_oth_26*g_oth_26</f>
@@ -45415,10 +45761,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">SUM(D5:D12)/1000</f>
@@ -45439,10 +45785,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>716</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>715</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">D13*hbm_gross</f>
@@ -45463,10 +45809,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D15" s="17" t="n">
         <f aca="false">u_bw_26+u_rb_26+u_ru_26+u_hp_26+u_amd_26+u_tpu_26+u_trn_26+u_oth_26</f>
@@ -45481,15 +45827,15 @@
         <v>26.5</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D16" s="16" t="n">
         <f aca="false">D13*1000/D15</f>
@@ -45506,10 +45852,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">D17/(1+hbm_g26)</f>
@@ -45532,12 +45878,12 @@
         <v>11.477169466875</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>223</v>
@@ -45557,12 +45903,12 @@
         <v>1</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>223</v>
@@ -45582,12 +45928,12 @@
         <v>0.85</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>223</v>
@@ -45607,15 +45953,15 @@
         <v>0.6</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">D14*D18</f>
@@ -45636,10 +45982,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">D14*D19</f>
@@ -45660,10 +46006,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D23" s="14" t="n">
         <f aca="false">D14*D20</f>
@@ -45684,10 +46030,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">C17</f>
@@ -45710,15 +46056,15 @@
         <v>11.477169466875</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">C17</f>
@@ -45743,10 +46089,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">C17</f>
@@ -45771,10 +46117,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D27" s="14" t="n">
         <f aca="false">D21-D17</f>
@@ -45795,10 +46141,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">D22-D17</f>
@@ -45819,10 +46165,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D29" s="14" t="n">
         <f aca="false">D23-D17</f>
@@ -45843,10 +46189,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C30" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -45871,10 +46217,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -45899,10 +46245,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -45927,10 +46273,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">C24*C30</f>
@@ -45955,10 +46301,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">C25*C31</f>
@@ -45983,10 +46329,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">C26*C32</f>
@@ -46011,15 +46357,15 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">(D5+D6+D7+D8)/1000*hbm_p26</f>
@@ -46028,22 +46374,22 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">nv_dc26*nv_hbm/nv_content</f>
         <v>38.9728971962617</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>49</v>
@@ -46055,10 +46401,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D41" s="17" t="n">
         <f aca="false">nv_dc26/nv_content</f>
@@ -46069,15 +46415,15 @@
         <v>7.6</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">pub26_lo</f>
@@ -46094,7 +46440,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>49</v>
@@ -46133,7 +46479,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46141,36 +46487,36 @@
         <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>19.1</v>
@@ -46205,7 +46551,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">F4*0.68</f>
@@ -46230,7 +46576,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F6" s="14" t="n">
         <f aca="false">F4*0.32</f>
@@ -46255,7 +46601,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">F4-F5-F6</f>
@@ -46280,7 +46626,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">F4*(1-0.745-0.07)</f>
@@ -46305,7 +46651,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">F4-F8-F10</f>
@@ -46330,7 +46676,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>3.1</v>
@@ -46365,7 +46711,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IF(B4=0,"",B10/B4)</f>
@@ -46406,7 +46752,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>8</v>
@@ -46441,7 +46787,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>5</v>
@@ -46476,7 +46822,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G14" s="0" t="n">
         <v>1</v>
@@ -46492,7 +46838,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="G15" s="0" t="n">
         <v>1</v>
@@ -46508,17 +46854,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>51.7</v>
@@ -46541,7 +46887,7 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B22" s="20" t="n">
         <v>25.1</v>
@@ -46564,7 +46910,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B23" s="20" t="n">
         <v>5.9</v>
@@ -46587,7 +46933,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>3.4</v>
@@ -46607,7 +46953,7 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B25" s="20" t="n">
         <v>-7</v>
@@ -46627,7 +46973,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B26" s="20" t="n">
         <v>79.1</v>
@@ -46650,7 +46996,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B27" s="21" t="n">
         <f aca="false">B21+B22+B23+B24+B25-B26</f>
@@ -46675,17 +47021,17 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -46714,12 +47060,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46727,72 +47073,72 @@
         <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">SUM(Q!B4:E4)</f>
@@ -46841,7 +47187,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">Q!J5-C6</f>
@@ -46884,12 +47230,12 @@
         <v>158.582541988058</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">(Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26)*fx/1000</f>
@@ -46932,12 +47278,12 @@
         <v>75.3957801559872</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">Q!J6</f>
@@ -46982,7 +47328,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">Q!J7</f>
@@ -47027,7 +47373,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">C6/C4</f>
@@ -47072,7 +47418,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">SUM(Q!B13:E13)</f>
@@ -47121,7 +47467,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">w_c*(1+cb_1)+w_h*D31/C31+w_n*(1+nb_1)</f>
@@ -47162,7 +47508,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">Q!J8</f>
@@ -47205,12 +47551,12 @@
         <v>110.782148943506</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">Q!J9</f>
@@ -47255,7 +47601,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">SUM(Q!B10:E10)</f>
@@ -47304,7 +47650,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B14/B4</f>
@@ -47353,7 +47699,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">nm_rev_0</f>
@@ -47398,7 +47744,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">nm_op_0</f>
@@ -47443,7 +47789,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">C4+C16</f>
@@ -47522,12 +47868,12 @@
         <v>557.69874365526</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">C14+C17</f>
@@ -47572,7 +47918,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">SUM(Q!B12:E12)</f>
@@ -47655,12 +48001,12 @@
         <v>57.927163053201</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">cap_0</f>
@@ -47705,7 +48051,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">C20+C10-C21</f>
@@ -47750,7 +48096,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">div_0</f>
@@ -47795,7 +48141,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">bb_0</f>
@@ -47838,12 +48184,12 @@
         <v>61.2301176183749</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">eq_last+(Q!H12+Q!I12)+extra_eq-C24-C23</f>
@@ -47888,7 +48234,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">nc_last+(Q!H12+Q!I12)+(Q!H13+Q!I13)-capex_rem+extra_eq-C24-C23</f>
@@ -47933,7 +48279,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C27" s="17" t="n">
         <f aca="false">sh_last+extra_sh-bb_sh_0</f>
@@ -48014,7 +48360,7 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C28" s="23" t="n">
         <f aca="false">C25/C27*1000000</f>
@@ -48059,7 +48405,7 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C29" s="23" t="n">
         <f aca="false">C20/C27*1000000</f>
@@ -48140,7 +48486,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">C20/C25</f>
@@ -48185,7 +48531,7 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">(Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26)</f>
@@ -48230,7 +48576,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D32" s="19" t="n">
         <f aca="false">D18/C18-1</f>
@@ -48307,7 +48653,7 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">C20/C18</f>
@@ -48416,30 +48762,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48451,10 +48797,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E4" s="23" t="n">
         <f aca="false">Y!C28</f>
@@ -48471,17 +48817,17 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E5" s="23" t="n">
         <f aca="false">Y!C28</f>
@@ -48498,17 +48844,17 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E6" s="23" t="n">
         <f aca="false">Y!C28</f>
@@ -48532,10 +48878,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E7" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -48552,17 +48898,17 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E8" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -48579,17 +48925,17 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E9" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -48613,10 +48959,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">Y!G28</f>
@@ -48633,17 +48979,17 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E11" s="23" t="n">
         <f aca="false">Y!G28</f>
@@ -48660,17 +49006,17 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E12" s="23" t="n">
         <f aca="false">Y!G28</f>
@@ -48694,10 +49040,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E13" s="23" t="n">
         <f aca="false">Y!J28</f>
@@ -48714,17 +49060,17 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E14" s="23" t="n">
         <f aca="false">Y!J28</f>
@@ -48741,17 +49087,17 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E15" s="23" t="n">
         <f aca="false">Y!J28</f>
@@ -48775,10 +49121,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E16" s="23" t="n">
         <f aca="false">Y!E28</f>
@@ -48795,17 +49141,17 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E17" s="23" t="n">
         <f aca="false">Y!E28</f>
@@ -48822,17 +49168,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E18" s="23" t="n">
         <f aca="false">Y!E28</f>
@@ -48856,10 +49202,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E19" s="23" t="n">
         <f aca="false">Y!H28</f>
@@ -48876,17 +49222,17 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">Y!H28</f>
@@ -48903,17 +49249,17 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E21" s="23" t="n">
         <f aca="false">Y!H28</f>
@@ -48937,10 +49283,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E22" s="23" t="n">
         <f aca="false">Y!K28</f>
@@ -48957,17 +49303,17 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E23" s="23" t="n">
         <f aca="false">Y!K28</f>
@@ -48984,17 +49330,17 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B24" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E24" s="23" t="n">
         <f aca="false">Y!K28</f>
@@ -49018,10 +49364,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E25" s="23" t="n">
         <f aca="false">Y!F28</f>
@@ -49038,17 +49384,17 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E26" s="23" t="n">
         <f aca="false">Y!F28</f>
@@ -49065,17 +49411,17 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E27" s="23" t="n">
         <f aca="false">Y!F28</f>
@@ -49099,10 +49445,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E28" s="23" t="n">
         <f aca="false">Y!I28</f>
@@ -49119,17 +49465,17 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B29" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E29" s="23" t="n">
         <f aca="false">Y!I28</f>
@@ -49146,17 +49492,17 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E30" s="23" t="n">
         <f aca="false">Y!I28</f>
@@ -49180,10 +49526,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E31" s="23" t="n">
         <f aca="false">Y!L28</f>
@@ -49200,17 +49546,17 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E32" s="23" t="n">
         <f aca="false">Y!L28</f>
@@ -49227,17 +49573,17 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E33" s="23" t="n">
         <f aca="false">Y!L28</f>
@@ -49261,10 +49607,10 @@
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E34" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -49288,10 +49634,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E35" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -49315,10 +49661,10 @@
         <v>12</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E36" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -49342,10 +49688,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E37" s="23" t="n">
         <f aca="false">Y!G29</f>
@@ -49369,10 +49715,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E38" s="23" t="n">
         <f aca="false">Y!G29</f>
@@ -49396,10 +49742,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E39" s="23" t="n">
         <f aca="false">Y!G29</f>
@@ -49423,10 +49769,10 @@
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E40" s="23" t="n">
         <f aca="false">Y!J29</f>
@@ -49450,10 +49796,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E41" s="23" t="n">
         <f aca="false">Y!J29</f>
@@ -49477,10 +49823,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E42" s="23" t="n">
         <f aca="false">Y!J29</f>
@@ -49504,10 +49850,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E43" s="23" t="n">
         <f aca="false">Y!E29</f>
@@ -49531,10 +49877,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E44" s="23" t="n">
         <f aca="false">Y!E29</f>
@@ -49558,10 +49904,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E45" s="23" t="n">
         <f aca="false">Y!E29</f>
@@ -49585,10 +49931,10 @@
         <v>4</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E46" s="23" t="n">
         <f aca="false">Y!H29</f>
@@ -49612,10 +49958,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E47" s="23" t="n">
         <f aca="false">Y!H29</f>
@@ -49639,10 +49985,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E48" s="23" t="n">
         <f aca="false">Y!H29</f>
@@ -49666,10 +50012,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E49" s="23" t="n">
         <f aca="false">Y!K29</f>
@@ -49693,10 +50039,10 @@
         <v>8</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E50" s="23" t="n">
         <f aca="false">Y!K29</f>
@@ -49720,10 +50066,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E51" s="23" t="n">
         <f aca="false">Y!K29</f>
@@ -49747,10 +50093,10 @@
         <v>4</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E52" s="23" t="n">
         <f aca="false">Y!F29</f>
@@ -49774,10 +50120,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">Y!F29</f>
@@ -49801,10 +50147,10 @@
         <v>12</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E54" s="23" t="n">
         <f aca="false">Y!F29</f>
@@ -49828,10 +50174,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E55" s="23" t="n">
         <f aca="false">Y!I29</f>
@@ -49855,10 +50201,10 @@
         <v>8</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E56" s="23" t="n">
         <f aca="false">Y!I29</f>
@@ -49882,10 +50228,10 @@
         <v>12</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E57" s="23" t="n">
         <f aca="false">Y!I29</f>
@@ -49909,10 +50255,10 @@
         <v>4</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E58" s="23" t="n">
         <f aca="false">Y!L29</f>
@@ -49936,10 +50282,10 @@
         <v>8</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E59" s="23" t="n">
         <f aca="false">Y!L29</f>
@@ -49963,10 +50309,10 @@
         <v>12</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E60" s="23" t="n">
         <f aca="false">Y!L29</f>
@@ -49983,55 +50329,55 @@
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B68" s="18" t="n">
         <v>1.27</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B69" s="18" t="n">
         <v>1.59</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B70" s="18" t="n">
         <v>1.04</v>
@@ -50039,7 +50385,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B71" s="18" t="n">
         <v>1.41</v>
@@ -50047,7 +50393,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B72" s="18" t="n">
         <v>1.97</v>
@@ -50055,7 +50401,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B73" s="18" t="n">
         <v>1.73</v>
@@ -50063,7 +50409,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B74" s="18" t="n">
         <v>1.04</v>
@@ -50071,7 +50417,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B75" s="18" t="n">
         <v>1.43</v>
@@ -50079,7 +50425,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B76" s="18" t="n">
         <v>0.8865</v>
@@ -50087,7 +50433,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B77" s="18" t="n">
         <v>1.96</v>
@@ -50095,7 +50441,7 @@
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B78" s="14" t="n">
         <f aca="false">PERCENTILE(B68:B77,0.25)</f>
@@ -50104,7 +50450,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B79" s="14" t="n">
         <f aca="false">MEDIAN(B68:B77)</f>
@@ -50113,7 +50459,7 @@
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B80" s="14" t="n">
         <f aca="false">PERCENTILE(B68:B77,0.75)</f>
@@ -50122,7 +50468,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B81" s="14" t="n">
         <f aca="false">MIN(B68:B77)</f>
@@ -50131,7 +50477,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B82" s="14" t="n">
         <f aca="false">MAX(B68:B77)</f>
@@ -50140,7 +50486,7 @@
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B83" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B78),2)</f>
@@ -50149,7 +50495,7 @@
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B84" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B79),2)</f>
@@ -50158,7 +50504,7 @@
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B85" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B80),2)</f>
@@ -50167,7 +50513,7 @@
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B86" s="14" t="n">
         <f aca="false">ROUND(MIN(B81),2)</f>
@@ -50176,7 +50522,7 @@
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B87" s="14" t="n">
         <f aca="false">ROUND(MAX(B82),2)</f>
@@ -50185,48 +50531,48 @@
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C91" s="14" t="n">
         <f aca="false">B83</f>
         <v>1.1</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E91" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -50247,17 +50593,17 @@
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C92" s="14" t="n">
         <f aca="false">B84</f>
         <v>1.42</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E92" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -50278,17 +50624,17 @@
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C93" s="14" t="n">
         <f aca="false">B85</f>
         <v>1.7</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E93" s="23" t="n">
         <f aca="false">Y!K28</f>
@@ -50309,48 +50655,48 @@
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B98" s="18" t="n">
         <v>9.15</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B99" s="18" t="n">
         <v>6.95</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B100" s="18" t="n">
         <v>5.06</v>
@@ -50358,7 +50704,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B101" s="18" t="n">
         <v>15.3</v>
@@ -50366,7 +50712,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B102" s="18" t="n">
         <v>19.1</v>
@@ -50374,7 +50720,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B103" s="18" t="n">
         <v>12.5</v>
@@ -50385,7 +50731,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B104" s="18" t="n">
         <v>6.5</v>
@@ -50396,7 +50742,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B105" s="18" t="n">
         <v>36.1</v>
@@ -50407,7 +50753,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B106" s="18" t="n">
         <v>10.6</v>
@@ -50418,7 +50764,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B107" s="18" t="n">
         <v>18.2</v>
@@ -50429,7 +50775,7 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B108" s="14" t="n">
         <f aca="false">PERCENTILE(B98:B107,0.25)</f>
@@ -50442,7 +50788,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B109" s="14" t="n">
         <f aca="false">MEDIAN(B98:B107)</f>
@@ -50455,7 +50801,7 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B110" s="14" t="n">
         <f aca="false">PERCENTILE(B98:B107,0.75)</f>
@@ -50468,7 +50814,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B111" s="14" t="n">
         <f aca="false">MIN(B98:B107)</f>
@@ -50481,7 +50827,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B112" s="14" t="n">
         <f aca="false">MAX(B98:B107)</f>
@@ -50494,7 +50840,7 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B113" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B108),2)</f>
@@ -50503,7 +50849,7 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B114" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B109),2)</f>
@@ -50512,7 +50858,7 @@
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B115" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B110),2)</f>
@@ -50521,7 +50867,7 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B116" s="14" t="n">
         <f aca="false">ROUND(MIN(B111),2)</f>
@@ -50530,7 +50876,7 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B117" s="14" t="n">
         <f aca="false">ROUND(MAX(B112),2)</f>
@@ -50539,48 +50885,48 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C121" s="14" t="n">
         <f aca="false">B113</f>
         <v>7.5</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E121" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -50601,17 +50947,17 @@
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C122" s="14" t="n">
         <f aca="false">B114</f>
         <v>11.55</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E122" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -50632,17 +50978,17 @@
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C123" s="14" t="n">
         <f aca="false">B115</f>
         <v>17.48</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E123" s="23" t="n">
         <f aca="false">Y!K29</f>
@@ -50663,12 +51009,12 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50676,29 +51022,29 @@
         <v>28</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B130" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -50715,7 +51061,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B131" s="23" t="n">
         <f aca="false">Y!E29</f>
@@ -50732,7 +51078,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B132" s="23" t="n">
         <f aca="false">Y!F29</f>
@@ -50749,7 +51095,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B133" s="23" t="n">
         <f aca="false">Y!M29</f>
@@ -50766,7 +51112,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B134" s="23" t="n">
         <f aca="false">Y!N29</f>
@@ -50783,7 +51129,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B135" s="23" t="n">
         <f aca="false">Y!O29</f>
@@ -50800,27 +51146,27 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B137" s="19" t="n">
         <f aca="false">MIN(tp_g/tp_roe,0.8)</f>
         <v>0.49813200498132</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B138" s="23" t="n">
         <f aca="false">Y!D22/Y!D27*1000000</f>
@@ -50837,7 +51183,7 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B139" s="23" t="n">
         <f aca="false">Y!E22/Y!E27*1000000</f>
@@ -50854,7 +51200,7 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B140" s="23" t="n">
         <f aca="false">Y!F22/Y!F27*1000000</f>
@@ -50871,7 +51217,7 @@
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B141" s="23" t="n">
         <f aca="false">B133*(1-$B$137)</f>
@@ -50888,7 +51234,7 @@
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B142" s="23" t="n">
         <f aca="false">B134*(1-$B$137)</f>
@@ -50905,7 +51251,7 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B143" s="23" t="n">
         <f aca="false">B135*(1-$B$137)</f>
@@ -50922,7 +51268,7 @@
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B144" s="23" t="n">
         <f aca="false">SUMPRODUCT(B138:B143,1/(1+tp_r)^{1;2;3;4;5;6})+B143*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -50937,12 +51283,12 @@
         <v>198984.090272765</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B145" s="23" t="n">
         <f aca="false">B144*(1+tp_r)</f>
@@ -50959,36 +51305,36 @@
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B146" s="27" t="n">
         <f aca="false">tp_wA*B145+tp_wB*C145+tp_wC*D145</f>
         <v>486542.246351878</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>33</v>
@@ -50996,19 +51342,19 @@
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C150" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>66</v>
@@ -51016,19 +51362,19 @@
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C151" s="18" t="n">
         <v>3.35</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>66</v>
@@ -51036,19 +51382,19 @@
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C152" s="18" t="n">
         <v>2.22</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>66</v>
@@ -51056,19 +51402,19 @@
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C153" s="18" t="n">
         <v>1.66</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>66</v>
@@ -51076,55 +51422,55 @@
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B154" s="14" t="n">
         <f aca="false">MEDIAN(C150:C153)</f>
         <v>1.94</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B155" s="23" t="n">
         <f aca="false">tp_wA*Y!E28+tp_wB*Y!H28+tp_wC*Y!K28</f>
         <v>241105.206895339</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B156" s="27" t="n">
         <f aca="false">B154*B155</f>
         <v>467744.101376957</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B157" s="23" t="n">
         <f aca="false">tp_wA*(2/12*Y!D29+10/12*Y!E29)+tp_wB*(2/12*Y!G29+10/12*Y!H29)+tp_wC*(2/12*Y!J29+10/12*Y!K29)</f>
         <v>78917.4698331062</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="6" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51132,29 +51478,29 @@
         <v>28</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
       <c r="E160" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B161" s="27" t="n">
         <f aca="false">tp_w_dcf*B146+(1-tp_w_dcf)*B156</f>
         <v>477143.173864418</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B162" s="23" t="n">
         <f aca="false">B156</f>
@@ -51163,31 +51509,31 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B163" s="23" t="n">
         <f aca="false">cons_tp</f>
         <v>478906</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B164" s="19" t="n">
         <f aca="false">B161/px-1</f>
         <v>1.21412145644741</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B165" s="19" t="n">
         <f aca="false">B162/px-1</f>
@@ -51196,7 +51542,7 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B166" s="28" t="n">
         <f aca="false">B145/px</f>
@@ -51211,36 +51557,36 @@
         <v>1.01569605243639</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B167" s="19" t="n">
         <f aca="false">B155/cons_bvps28-1</f>
         <v>0.0390002667270208</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B168" s="19" t="n">
         <f aca="false">B157/(2/12*cons_eps27+10/12*cons_eps28)-1</f>
         <v>0.0523872812426651</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B169" s="19" t="n">
         <f aca="false">(cons_tp/cons_bvps28)/B154-1</f>
@@ -51253,19 +51599,19 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B170" s="29" t="str">
         <f aca="false">TEXT(D145,"#,##0")&amp;"～"&amp;TEXT(B145,"#,##0")</f>
         <v>218,882～818,535</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B171" s="15" t="n">
         <f aca="false">IF(px/Y!E28&gt;=MAX($B$68:$B$77),1,IF(px/Y!E28&lt;=MIN($B$68:$B$77),0,PERCENTRANK($B$68:$B$77,px/Y!E28)))</f>
@@ -51280,12 +51626,12 @@
         <v>0.111</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B172" s="0" t="str">
         <f aca="false">"DCF：股東現金流 2027–2029 用每股（淨利＋折舊－資本支出；折舊與資本支出為記憶體事業口徑，淨利為合併），2030–2032 收斂期用 EPS ×（1 − g／ROE），r 10%、g 4%、ROE 為 2023–2025 平均約 8%（再投資率約五成）；明確期＋永續，基準日 2026 年底。Comparable：SK 海力士、美光、鎧俠、南亞科前瞻 P/B 中位數 × 2028 年底每"&amp;"股淨值（情境加權）。收斂期（2030–2032）淨利率收斂到循環中段：A 十年平均 × 1.2、B 十年平均、C 十年平均 × 0.8（In 頁 cyc_mA／cyc_mC），永續期以 2032 中段水準為基礎。偏誤：2027–2029 仍為高峰期盈餘且權重大，DCF 仍可能偏高估；純記憶體同業倍數未含集團折價，Comparable 偏高估。情境對應：A＝順利、B＝平平、C＝不如預期（原為 Tre"&amp;"ndForce／BofA 型價格情境）。"&amp;IF(MAX(B166:D166)&gt;3,"注意：DCF ÷ 現價有情境高於 3 倍（見上方「DCF ÷ 現價」列）；DCF 對收斂期淨利率與永續假設敏感，宜與 Comparable、市場共識並讀。","")</f>
@@ -51294,7 +51640,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51302,29 +51648,29 @@
         <v>28</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B176" s="23" t="n">
         <f aca="false">tp_wA*B178+tp_wB*B179+tp_wC*B180</f>
         <v>255831.994790815</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B177" s="19" t="n">
         <f aca="false">B176/px-1</f>
@@ -51333,7 +51679,7 @@
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B178" s="23" t="n">
         <f aca="false">B85*Y!D28</f>
@@ -51346,7 +51692,7 @@
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B179" s="23" t="n">
         <f aca="false">B84*Y!G28</f>
@@ -51359,7 +51705,7 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B180" s="23" t="n">
         <f aca="false">B83*Y!J28</f>
@@ -51372,7 +51718,7 @@
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B181" s="15" t="n">
         <f aca="false">tp_wA</f>
@@ -51393,34 +51739,34 @@
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B184" s="29" t="str">
         <f aca="false">IF(B164&gt;0.5,"大於 50%",IF(B164&gt;0.25,"25%–50%",IF(B164&gt;=0,"0%–25%",IF(B164&gt;=-0.25,"0%～−25%",IF(B164&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
         <v>大於 50%</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B185" s="29" t="str">
         <f aca="false">IF(B164&gt;0.5,"強力買進",IF(B164&gt;0.25,"買進",IF(B164&gt;=-0.25,"中立",IF(B164&gt;=-0.5,"放空","強力放空"))))</f>
         <v>強力買進</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
   </sheetData>
@@ -51448,29 +51794,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>31</v>
@@ -51482,10 +51828,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -51502,10 +51848,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -51522,10 +51868,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -51542,10 +51888,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -51562,10 +51908,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -51582,10 +51928,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -51602,7 +51948,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>31</v>
@@ -51614,10 +51960,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -51634,10 +51980,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -51654,10 +52000,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -51674,10 +52020,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -51694,10 +52040,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -51714,10 +52060,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -51734,7 +52080,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>31</v>
@@ -51746,10 +52092,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -51766,10 +52112,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -51786,10 +52132,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -51806,10 +52152,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -51826,10 +52172,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -51846,10 +52192,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -51866,7 +52212,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>31</v>
@@ -51878,10 +52224,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -51898,10 +52244,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -51918,10 +52264,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -51938,10 +52284,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -51958,10 +52304,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -51978,10 +52324,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -51998,32 +52344,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52031,7 +52377,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C40" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52052,10 +52398,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C41" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r+0.01))^1+Val!B139/(1+(tp_r+0.01))^2+Val!B140/(1+(tp_r+0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C138/(1+(tp_r+0.01))^1+Val!C139/(1+(tp_r+0.01))^2+Val!C140/(1+(tp_r+0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D138/(1+(tp_r+0.01))^1+Val!D139/(1+(tp_r+0.01))^2+Val!D140/(1+(tp_r+0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
@@ -52076,10 +52422,10 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C42" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r-0.01))^1+Val!B139/(1+(tp_r-0.01))^2+Val!B140/(1+(tp_r-0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C138/(1+(tp_r-0.01))^1+Val!C139/(1+(tp_r-0.01))^2+Val!C140/(1+(tp_r-0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D138/(1+(tp_r-0.01))^1+Val!D139/(1+(tp_r-0.01))^2+Val!D140/(1+(tp_r-0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
@@ -52100,10 +52446,10 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C43" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52124,10 +52470,10 @@
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C44" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52148,10 +52494,10 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C45" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52172,10 +52518,10 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C46" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52196,7 +52542,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C47" s="30" t="n">
         <f aca="false">C40-Val!B146</f>
@@ -52228,7 +52574,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52236,21 +52582,21 @@
         <v>28</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Q!H10+nm_op_q</f>
@@ -52264,12 +52610,12 @@
         <v>0.0383651864059591</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!C18</f>
@@ -52283,12 +52629,12 @@
         <v>0.0221156435576788</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!C19</f>
@@ -52302,12 +52648,12 @@
         <v>0.0516479449262781</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!C20</f>
@@ -52321,12 +52667,12 @@
         <v>0.0479415417578637</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!D19</f>
@@ -52340,12 +52686,12 @@
         <v>0.159533803455726</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -52359,12 +52705,12 @@
         <v>0.176122795889556</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!E19</f>
@@ -52378,12 +52724,12 @@
         <v>0.247012110688031</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -52398,12 +52744,12 @@
         <v>0.32575543502237</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -52418,12 +52764,12 @@
         <v>0.720912929388087</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">Y!E28</f>
@@ -52438,7 +52784,7 @@
         <v>0.241532090173527</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>

--- a/samsung/dist/20261028_三星電子個股模型_v0.3.2.xlsx
+++ b/samsung/dist/20261028_三星電子個股模型_v0.3.2.xlsx
@@ -420,6 +420,7 @@
     <definedName function="false" hidden="false" name="q4_np_hi" vbProcedure="false">In!$F$15</definedName>
     <definedName function="false" hidden="false" name="q4_np_lo" vbProcedure="false">In!$D$15</definedName>
     <definedName function="false" hidden="false" name="rf" vbProcedure="false">In!$E$45</definedName>
+    <definedName function="false" hidden="false" name="rm_factor" vbProcedure="false">Val!$B$203</definedName>
     <definedName function="false" hidden="false" name="sh25" vbProcedure="false">In!$E$29</definedName>
     <definedName function="false" hidden="false" name="sh25_hi" vbProcedure="false">In!$F$29</definedName>
     <definedName function="false" hidden="false" name="sh25_lo" vbProcedure="false">In!$D$29</definedName>
@@ -439,6 +440,7 @@
     <definedName function="false" hidden="false" name="tax" vbProcedure="false">In!$E$44</definedName>
     <definedName function="false" hidden="false" name="tax_hi" vbProcedure="false">In!$F$44</definedName>
     <definedName function="false" hidden="false" name="tax_lo" vbProcedure="false">In!$D$44</definedName>
+    <definedName function="false" hidden="false" name="tp_comp_adj" vbProcedure="false">Val!$B$204</definedName>
     <definedName function="false" hidden="false" name="tp_g" vbProcedure="false">In!$E$251</definedName>
     <definedName function="false" hidden="false" name="tp_r" vbProcedure="false">In!$E$250</definedName>
     <definedName function="false" hidden="false" name="tp_roe" vbProcedure="false">In!$E$252</definedName>
@@ -522,7 +524,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="1117">
   <si>
     <r>
       <rPr>
@@ -3584,45 +3586,45 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：目標價 ₩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">477,143</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF 486,542</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境價值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A 818,535</t>
     </r>
     <r>
       <rPr>
@@ -3641,92 +3643,504 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable 467,744 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">各半），比現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">215,500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">121.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，級距 大於 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
+      <t xml:space="preserve">B 394,410</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C 218,882</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（現價的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍），對應 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 EPS A 129,982</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B 59,278</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C 36,498</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；收斂期用的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ROE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平均 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，低於折現率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，再投資率約五成，壓低 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2030 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年後的股東現金流。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益對一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入最敏感（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±20% → ±15.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND ±30% → ±9.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM ±30% → ±7.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；折現率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±1pt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使加權目標價 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+5.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。下一個檢驗事件是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確定財報與法說（約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，日期未確認；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初步財報已納入）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：加權目標價中的 </t>
     </r>
     <r>
       <rPr>
@@ -3745,254 +4159,140 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">單獨為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+117.1%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。主因是倍數不是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：本模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年底每股淨值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">241,105 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">只比共識 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">232,055 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 78,917 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">比共識高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），但現價只隱含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.89 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P/B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，記憶體同業中位數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.94 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍、共識目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">478,906 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隱含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.06 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍；同業倍數未扣三星的集團折價，</t>
+      <t xml:space="preserve">改用相對倍數調整後的值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節：同業前瞻倍數中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的倍數比，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前瞻倍數；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「照建議做」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料取回）。「</t>
     </r>
     <r>
       <rPr>
@@ -4011,18 +4311,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">偏高估。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
+      <t xml:space="preserve">目標價（市場主流同業法）」維持不調整。重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的第一句已改為公式；重點觀察 </t>
     </r>
     <r>
       <rPr>
@@ -4041,44 +4349,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境價值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 818,535</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">、</t>
     </r>
     <r>
@@ -4089,483 +4359,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">B 394,410</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 218,882</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（現價的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.80</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.83</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.02 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍），對應 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 EPS A 129,982</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B 59,278</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 36,498</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；收斂期用的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ROE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2023–2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">平均 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，低於折現率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，再投資率約五成，壓低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2030 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年後的股東現金流。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益對一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入最敏感（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±20% → ±15.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND ±30% → ±9.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM ±30% → ±7.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；折現率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±1pt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">使加權目標價 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4.1%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+5.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。下一個檢驗事件是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">確定財報與法說（約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，日期未確認；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-08 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">初步財報已納入）。</t>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與其他說明中的目標價與上檔空間數字為調整前撰寫，以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁為準。</t>
     </r>
   </si>
   <si>
@@ -35559,116 +35381,13 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sens — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一次只動一個價格或份額輸入；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Δ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Δ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× (1 − </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業費用變動率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（成本只隨量變動，所以這是精確值，不是近似）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">欄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">輸入變動</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Cambria"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Δ</t>
+      <t xml:space="preserve">0.5 </t>
     </r>
     <r>
       <rPr>
@@ -35677,324 +35396,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營收</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">營業利益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相對基準</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（價格或份額）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">讀法：哪一條收入線的同幅變動對營業利益影響最大，就是該年度的主要驅動。價格路徑本身的情境差異見 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Y </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頁 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">欄。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標價參數（只改 </t>
+      <t xml:space="preserve">相對倍數調整（</t>
     </r>
     <r>
       <rPr>
@@ -36004,7 +35406,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">Comparable </t>
     </r>
     <r>
       <rPr>
@@ -36013,7 +35415,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">參數；</t>
+      <t xml:space="preserve">目標倍數＝同業中位數 </t>
     </r>
     <r>
       <rPr>
@@ -36023,7 +35425,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Y </t>
+      <t xml:space="preserve">× </t>
     </r>
     <r>
       <rPr>
@@ -36032,7 +35434,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">頁收斂法的 </t>
+      <t xml:space="preserve">本公司 </t>
     </r>
     <r>
       <rPr>
@@ -36042,7 +35444,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">fade_g </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -36051,7 +35453,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不隨 </t>
+      <t xml:space="preserve">年相對同業的 </t>
     </r>
     <r>
       <rPr>
@@ -36061,7 +35463,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tp_g </t>
+      <t xml:space="preserve">P/B </t>
     </r>
     <r>
       <rPr>
@@ -36070,16 +35472,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">變動）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">案例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">設定</t>
-  </si>
-  <si>
+      <t xml:space="preserve">比；</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -36088,7 +35482,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">Andy 2026-10-27 </t>
     </r>
     <r>
       <rPr>
@@ -36097,8 +35491,343 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">目標價</t>
-    </r>
+      <t xml:space="preserve">新增，放在本頁最後以免位移既有儲存格）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2017–2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各年度窗口（前一年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月～當年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/data/fwd_mult_hist.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Derived] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">彙總；有效值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，無效值以「剔除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」文字列示、不進中位數。本公司或同業有效年數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不納入；有效同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家或本公司不足時係數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/11–2017/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017/11–2018/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/11–2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11–2020/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020/11–2021/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/11–2022/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022/11–2023/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023/11–2024/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/11–2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11–2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效年數</t>
   </si>
   <si>
     <r>
@@ -36109,7 +35838,1196 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">納入值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">三星電子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">005930.KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 005930 KS Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">同業</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 000660 KS Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg MU US Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 285A JT Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 2408 TT Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數（納入值）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空白＝本公司有效年數不足</t>
+  </si>
+  <si>
+    <t xml:space="preserve">納入的同業家數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數的中位數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原始比值（本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝本公司長期比同業便宜（折價），＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝長期溢價</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值下限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避免單一歷史異常主導；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_LO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值上限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_HI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相對倍數調整係數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料不足時＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（相對倍數調整後）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調整係數；加權目標價使用本列</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sens — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一次只動一個價格或份額輸入；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× (1 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業費用變動率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（成本只隨量變動，所以這是精確值，不是近似）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">輸入變動</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">營業利益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相對基準</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（價格或份額）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">讀法：哪一條收入線的同幅變動對營業利益影響最大，就是該年度的主要驅動。價格路徑本身的情境差異見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Y </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">欄。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價參數（只改 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參數；</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Y </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁收斂法的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">fade_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不隨 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tp_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">變動）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">案例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
     </r>
     <r>
       <rPr>
@@ -38039,7 +38957,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -38157,6 +39075,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -38416,7 +39338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -38553,17 +39475,23 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>23</v>
+      <c r="A28" s="0" t="str">
+        <f aca="false">"重點觀察 1：目標價 ₩"&amp;TEXT(Val!$B$161,"#,##0")&amp;"（DCF "&amp;TEXT(Val!$B$146,"#,##0")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0")&amp;"（2026-10-23）"&amp;IF(Val!$B$164&gt;=0,"高 "&amp;TEXT(Val!$B$164,"0.0%"),"低 "&amp;TEXT(-Val!$B$164,"0.0%"))&amp;"，級距 "&amp;Val!$B$184&amp;"、投資建議 "&amp;Val!$B$185&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$146+(1-tp_w_dcf)*Val!$B$156)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$165,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是倍數不是 EPS：本模型 2028 年底每股淨值 241,105 只比共識 232,055 高 3.9%（前瞻 EPS 78,917 比共識高 5.2%），但現價只隱含 0.89 倍前瞻 P/B，記憶體同業中位數 1.94 倍、共識目標價 478,906 隱含 2.06 倍；同業倍數未扣三星的集團折價，Comparab"&amp;"le 偏高估。"</f>
+        <v>重點觀察 1：目標價 ₩485,941（DCF 486,542、Comparable（相對倍數調整後）485,340；DCF 權重 50%），比現價 215,500（2026-10-23）高 125.5%，級距 大於 50%、投資建議 強力買進。相對倍數調整係數 1.04（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 +121.4%；Comparable 單獨（市場主流同業法、未調整）為 +117.1%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是倍數不是 EPS：本模型 2028 年底每股淨值 241,105 只比共識 232,055 高 3.9%（前瞻 EPS 78,917 比共識高 5.2%），但現價只隱含 0.89 倍前瞻 P/B，記憶體同業中位數 1.94 倍、共識目標價 478,906 隱含 2.06 倍；同業倍數未扣三星的集團折價，Comparable 偏高估。</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
         <v>25</v>
       </c>
     </row>
@@ -38592,12 +39520,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1045</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1046</v>
+        <v>1085</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
@@ -38609,7 +39537,7 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1047</v>
+        <v>1086</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
@@ -38621,7 +39549,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1048</v>
+        <v>1087</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
@@ -38633,7 +39561,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1049</v>
+        <v>1088</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
@@ -38645,13 +39573,13 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1050</v>
+        <v>1089</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1051</v>
+        <v>1090</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>1052</v>
+        <v>1091</v>
       </c>
     </row>
   </sheetData>
@@ -38684,106 +39612,106 @@
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1053</v>
+        <v>1092</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1054</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1055</v>
+        <v>1094</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1056</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1057</v>
+        <v>1096</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1058</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1059</v>
+        <v>1098</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1060</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1062</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1063</v>
+        <v>1102</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1064</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1065</v>
+        <v>1104</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1066</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1067</v>
+        <v>1106</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1068</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1069</v>
+        <v>1108</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1070</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1071</v>
+        <v>1110</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1072</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1073</v>
+        <v>1112</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1074</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1075</v>
+        <v>1114</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1076</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>1077</v>
+        <v>1116</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1076</v>
+        <v>1115</v>
       </c>
     </row>
   </sheetData>
@@ -48748,7 +49676,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -51491,8 +52419,8 @@
         <v>958</v>
       </c>
       <c r="B161" s="27" t="n">
-        <f aca="false">tp_w_dcf*B146+(1-tp_w_dcf)*B156</f>
-        <v>477143.173864418</v>
+        <f aca="false">tp_w_dcf*B146+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>485941.016044813</v>
       </c>
       <c r="E161" s="8" t="s">
         <v>959</v>
@@ -51525,7 +52453,7 @@
       </c>
       <c r="B164" s="19" t="n">
         <f aca="false">B161/px-1</f>
-        <v>1.21412145644741</v>
+        <v>1.25494671018475</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>963</v>
@@ -51767,6 +52695,413 @@
       </c>
       <c r="E185" s="4" t="s">
         <v>990</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="6" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="E190" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="F190" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="G190" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="H190" s="13" t="s">
+        <v>999</v>
+      </c>
+      <c r="I190" s="13" t="s">
+        <v>1000</v>
+      </c>
+      <c r="J190" s="13" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K190" s="13" t="s">
+        <v>1002</v>
+      </c>
+      <c r="L190" s="13" t="s">
+        <v>1003</v>
+      </c>
+      <c r="M190" s="13" t="s">
+        <v>1004</v>
+      </c>
+      <c r="N190" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="O190" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P190" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q190" s="5" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B191" s="0" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D191" s="18" t="n">
+        <v>1.4135</v>
+      </c>
+      <c r="E191" s="18" t="n">
+        <v>1.2645</v>
+      </c>
+      <c r="F191" s="18" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="G191" s="18" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="H191" s="18" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="I191" s="18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J191" s="18" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="K191" s="18" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="L191" s="18" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="M191" s="18" t="n">
+        <v>1.8275</v>
+      </c>
+      <c r="N191" s="8" t="n">
+        <f aca="false">COUNT(D191:M191)</f>
+        <v>10</v>
+      </c>
+      <c r="O191" s="14" t="n">
+        <f aca="false">IF(N191&gt;0,MEDIAN(D191:M191),"")</f>
+        <v>1.2895</v>
+      </c>
+      <c r="P191" s="14" t="n">
+        <f aca="false">IF(N191&gt;=7,O191,"")</f>
+        <v>1.2895</v>
+      </c>
+      <c r="Q191" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="0" t="s">
+        <v>934</v>
+      </c>
+      <c r="B192" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D192" s="18" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="E192" s="18" t="n">
+        <v>1.1395</v>
+      </c>
+      <c r="F192" s="18" t="n">
+        <v>0.9995</v>
+      </c>
+      <c r="G192" s="18" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="H192" s="18" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="I192" s="18" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="J192" s="18" t="n">
+        <v>1.2725</v>
+      </c>
+      <c r="K192" s="18" t="n">
+        <v>1.6605</v>
+      </c>
+      <c r="L192" s="18" t="n">
+        <v>1.3995</v>
+      </c>
+      <c r="M192" s="18" t="n">
+        <v>2.3405</v>
+      </c>
+      <c r="N192" s="8" t="n">
+        <f aca="false">COUNT(D192:M192)</f>
+        <v>10</v>
+      </c>
+      <c r="O192" s="14" t="n">
+        <f aca="false">IF(N192&gt;0,MEDIAN(D192:M192),"")</f>
+        <v>1.24275</v>
+      </c>
+      <c r="P192" s="14" t="n">
+        <f aca="false">IF(N192&gt;=7,O192,"")</f>
+        <v>1.24275</v>
+      </c>
+      <c r="Q192" s="8" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="B193" s="0" t="s">
+        <v>939</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D193" s="18" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E193" s="18" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="F193" s="18" t="n">
+        <v>1.2295</v>
+      </c>
+      <c r="G193" s="18" t="n">
+        <v>1.3335</v>
+      </c>
+      <c r="H193" s="18" t="n">
+        <v>1.802</v>
+      </c>
+      <c r="I193" s="18" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="J193" s="18" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="K193" s="18" t="n">
+        <v>2.1515</v>
+      </c>
+      <c r="L193" s="18" t="n">
+        <v>1.898</v>
+      </c>
+      <c r="M193" s="18" t="n">
+        <v>3.5655</v>
+      </c>
+      <c r="N193" s="8" t="n">
+        <f aca="false">COUNT(D193:M193)</f>
+        <v>10</v>
+      </c>
+      <c r="O193" s="14" t="n">
+        <f aca="false">IF(N193&gt;0,MEDIAN(D193:M193),"")</f>
+        <v>1.62</v>
+      </c>
+      <c r="P193" s="14" t="n">
+        <f aca="false">IF(N193&gt;=7,O193,"")</f>
+        <v>1.62</v>
+      </c>
+      <c r="Q193" s="8" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="B194" s="0" t="s">
+        <v>942</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="L194" s="18" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="M194" s="18" t="n">
+        <v>3.9425</v>
+      </c>
+      <c r="N194" s="8" t="n">
+        <f aca="false">COUNT(D194:M194)</f>
+        <v>2</v>
+      </c>
+      <c r="O194" s="14" t="n">
+        <f aca="false">IF(N194&gt;0,MEDIAN(D194:M194),"")</f>
+        <v>2.71825</v>
+      </c>
+      <c r="P194" s="14" t="str">
+        <f aca="false">IF(N194&gt;=7,O194,"")</f>
+        <v/>
+      </c>
+      <c r="Q194" s="8" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="B195" s="0" t="s">
+        <v>946</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D195" s="18" t="n">
+        <v>1.4325</v>
+      </c>
+      <c r="E195" s="18" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="F195" s="18" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="G195" s="18" t="n">
+        <v>1.1455</v>
+      </c>
+      <c r="H195" s="18" t="n">
+        <v>1.3955</v>
+      </c>
+      <c r="I195" s="18" t="n">
+        <v>1.0635</v>
+      </c>
+      <c r="J195" s="18" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="K195" s="18" t="n">
+        <v>1.1785</v>
+      </c>
+      <c r="L195" s="18" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="M195" s="18" t="n">
+        <v>2.7665</v>
+      </c>
+      <c r="N195" s="8" t="n">
+        <f aca="false">COUNT(D195:M195)</f>
+        <v>10</v>
+      </c>
+      <c r="O195" s="14" t="n">
+        <f aca="false">IF(N195&gt;0,MEDIAN(D195:M195),"")</f>
+        <v>1.199</v>
+      </c>
+      <c r="P195" s="14" t="n">
+        <f aca="false">IF(N195&gt;=7,O195,"")</f>
+        <v>1.199</v>
+      </c>
+      <c r="Q195" s="8" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B197" s="14" t="n">
+        <f aca="false">P191</f>
+        <v>1.2895</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B198" s="16" t="n">
+        <f aca="false">COUNT(P192:P195)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B199" s="14" t="n">
+        <f aca="false">IF(B198&gt;0,MEDIAN(P192:P195),"")</f>
+        <v>1.24275</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B200" s="14" t="n">
+        <f aca="false">IF(AND(ISNUMBER(B197),B198&gt;=2),B197/B199,"")</f>
+        <v>1.03761818547576</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B201" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B202" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B203" s="30" t="n">
+        <f aca="false">IF(ISNUMBER(B200),MIN(MAX(B200,B201),B202),1)</f>
+        <v>1.03761818547576</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B204" s="27" t="n">
+        <f aca="false">Val!$B$156*B203</f>
+        <v>485339.785737748</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
@@ -51794,24 +53129,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>991</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>992</v>
+        <v>1032</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>993</v>
+        <v>1033</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>994</v>
+        <v>1034</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>995</v>
+        <v>1035</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>996</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51831,7 +53166,7 @@
         <v>784</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -51851,7 +53186,7 @@
         <v>784</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>998</v>
+        <v>1038</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -51871,7 +53206,7 @@
         <v>784</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>999</v>
+        <v>1039</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -51891,7 +53226,7 @@
         <v>784</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -51911,7 +53246,7 @@
         <v>784</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1001</v>
+        <v>1041</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -51931,7 +53266,7 @@
         <v>784</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1002</v>
+        <v>1042</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -51963,7 +53298,7 @@
         <v>788</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -51983,7 +53318,7 @@
         <v>788</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>998</v>
+        <v>1038</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -52003,7 +53338,7 @@
         <v>788</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>999</v>
+        <v>1039</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -52023,7 +53358,7 @@
         <v>788</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -52043,7 +53378,7 @@
         <v>788</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1001</v>
+        <v>1041</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -52063,7 +53398,7 @@
         <v>788</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1002</v>
+        <v>1042</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -52095,7 +53430,7 @@
         <v>791</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -52115,7 +53450,7 @@
         <v>791</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>998</v>
+        <v>1038</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -52135,7 +53470,7 @@
         <v>791</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>999</v>
+        <v>1039</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -52155,7 +53490,7 @@
         <v>791</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -52175,7 +53510,7 @@
         <v>791</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1001</v>
+        <v>1041</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -52195,7 +53530,7 @@
         <v>791</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1002</v>
+        <v>1042</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -52227,7 +53562,7 @@
         <v>792</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -52247,7 +53582,7 @@
         <v>792</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>998</v>
+        <v>1038</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -52267,7 +53602,7 @@
         <v>792</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>999</v>
+        <v>1039</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -52287,7 +53622,7 @@
         <v>792</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -52307,7 +53642,7 @@
         <v>792</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1001</v>
+        <v>1041</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -52327,7 +53662,7 @@
         <v>792</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1002</v>
+        <v>1042</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -52344,32 +53679,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>1003</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>1004</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>1005</v>
+        <v>1045</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>1006</v>
+        <v>1046</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1007</v>
+        <v>1047</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>1008</v>
+        <v>1029</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1009</v>
+        <v>1048</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>996</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52377,19 +53712,19 @@
         <v>31</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1010</v>
+        <v>1049</v>
       </c>
       <c r="C40" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>486542.246351878</v>
       </c>
       <c r="D40" s="23" t="n">
-        <f aca="false">Val!B156</f>
-        <v>467744.101376957</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>485339.785737748</v>
       </c>
       <c r="E40" s="23" t="n">
         <f aca="false">tp_w_dcf*C40+(1-tp_w_dcf)*D40</f>
-        <v>477143.173864418</v>
+        <v>485941.016044813</v>
       </c>
       <c r="F40" s="19" t="n">
         <f aca="false">E40/E$40-1</f>
@@ -52398,153 +53733,153 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>1011</v>
+        <v>1050</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1012</v>
+        <v>1051</v>
       </c>
       <c r="C41" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r+0.01))^1+Val!B139/(1+(tp_r+0.01))^2+Val!B140/(1+(tp_r+0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C138/(1+(tp_r+0.01))^1+Val!C139/(1+(tp_r+0.01))^2+Val!C140/(1+(tp_r+0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D138/(1+(tp_r+0.01))^1+Val!D139/(1+(tp_r+0.01))^2+Val!D140/(1+(tp_r+0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
         <v>447679.293922178</v>
       </c>
       <c r="D41" s="23" t="n">
-        <f aca="false">Val!B156</f>
-        <v>467744.101376957</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>485339.785737748</v>
       </c>
       <c r="E41" s="23" t="n">
         <f aca="false">tp_w_dcf*C41+(1-tp_w_dcf)*D41</f>
-        <v>457711.697649568</v>
+        <v>466509.539829963</v>
       </c>
       <c r="F41" s="19" t="n">
         <f aca="false">E41/E$40-1</f>
-        <v>-0.0407246237171813</v>
+        <v>-0.0399873144543494</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>1013</v>
+        <v>1052</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1014</v>
+        <v>1053</v>
       </c>
       <c r="C42" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r-0.01))^1+Val!B139/(1+(tp_r-0.01))^2+Val!B140/(1+(tp_r-0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C138/(1+(tp_r-0.01))^1+Val!C139/(1+(tp_r-0.01))^2+Val!C140/(1+(tp_r-0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D138/(1+(tp_r-0.01))^1+Val!D139/(1+(tp_r-0.01))^2+Val!D140/(1+(tp_r-0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
         <v>540048.095642413</v>
       </c>
       <c r="D42" s="23" t="n">
-        <f aca="false">Val!B156</f>
-        <v>467744.101376957</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>485339.785737748</v>
       </c>
       <c r="E42" s="23" t="n">
         <f aca="false">tp_w_dcf*C42+(1-tp_w_dcf)*D42</f>
-        <v>503896.098509685</v>
+        <v>512693.940690081</v>
       </c>
       <c r="F42" s="19" t="n">
         <f aca="false">E42/E$40-1</f>
-        <v>0.0560689665296761</v>
+        <v>0.0550538517267296</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>1015</v>
+        <v>1054</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1016</v>
+        <v>1055</v>
       </c>
       <c r="C43" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>453788.933116681</v>
       </c>
       <c r="D43" s="23" t="n">
-        <f aca="false">Val!B156</f>
-        <v>467744.101376957</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>485339.785737748</v>
       </c>
       <c r="E43" s="23" t="n">
         <f aca="false">tp_w_dcf*C43+(1-tp_w_dcf)*D43</f>
-        <v>460766.517246819</v>
+        <v>469564.359427215</v>
       </c>
       <c r="F43" s="19" t="n">
         <f aca="false">E43/E$40-1</f>
-        <v>-0.034322311445772</v>
+        <v>-0.033700914466723</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>1017</v>
+        <v>1056</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1018</v>
+        <v>1057</v>
       </c>
       <c r="C44" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>513605.057050687</v>
       </c>
       <c r="D44" s="23" t="n">
-        <f aca="false">Val!B156</f>
-        <v>467744.101376957</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>485339.785737748</v>
       </c>
       <c r="E44" s="23" t="n">
         <f aca="false">tp_w_dcf*C44+(1-tp_w_dcf)*D44</f>
-        <v>490674.579213822</v>
+        <v>499472.421394218</v>
       </c>
       <c r="F44" s="19" t="n">
         <f aca="false">E44/E$40-1</f>
-        <v>0.0283592139437157</v>
+        <v>0.0278457773734349</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1019</v>
+        <v>1058</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1020</v>
+        <v>1059</v>
       </c>
       <c r="C45" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>486542.246351878</v>
       </c>
       <c r="D45" s="23" t="n">
-        <f aca="false">Val!B156</f>
-        <v>467744.101376957</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>485339.785737748</v>
       </c>
       <c r="E45" s="23" t="n">
         <f aca="false">0.3*C45+(1-0.3)*D45</f>
-        <v>473383.544869434</v>
+        <v>485700.523921987</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">E45/E$40-1</f>
-        <v>-0.00787945673524937</v>
+        <v>-0.000494899822993999</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1021</v>
+        <v>1060</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1022</v>
+        <v>1061</v>
       </c>
       <c r="C46" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>486542.246351878</v>
       </c>
       <c r="D46" s="23" t="n">
-        <f aca="false">Val!B156</f>
-        <v>467744.101376957</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>485339.785737748</v>
       </c>
       <c r="E46" s="23" t="n">
         <f aca="false">0.7*C46+(1-0.7)*D46</f>
-        <v>480902.802859402</v>
+        <v>486181.508167639</v>
       </c>
       <c r="F46" s="19" t="n">
         <f aca="false">E46/E$40-1</f>
-        <v>0.00787945673524937</v>
+        <v>0.000494899822993888</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C47" s="30" t="n">
+        <v>1062</v>
+      </c>
+      <c r="C47" s="31" t="n">
         <f aca="false">C40-Val!B146</f>
         <v>0</v>
       </c>
@@ -52574,7 +53909,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1024</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52582,21 +53917,21 @@
         <v>28</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1025</v>
+        <v>1064</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1026</v>
+        <v>1065</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1027</v>
+        <v>1066</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1028</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1029</v>
+        <v>1068</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Q!H10+nm_op_q</f>
@@ -52610,12 +53945,12 @@
         <v>0.0383651864059591</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1030</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1031</v>
+        <v>1070</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!C18</f>
@@ -52629,12 +53964,12 @@
         <v>0.0221156435576788</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1032</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1033</v>
+        <v>1072</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!C19</f>
@@ -52648,12 +53983,12 @@
         <v>0.0516479449262781</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1034</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1035</v>
+        <v>1074</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!C20</f>
@@ -52667,12 +54002,12 @@
         <v>0.0479415417578637</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1036</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1037</v>
+        <v>1076</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!D19</f>
@@ -52686,12 +54021,12 @@
         <v>0.159533803455726</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1038</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1039</v>
+        <v>1078</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -52705,12 +54040,12 @@
         <v>0.176122795889556</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1036</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1040</v>
+        <v>1079</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!E19</f>
@@ -52724,12 +54059,12 @@
         <v>0.247012110688031</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1041</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1042</v>
+        <v>1081</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -52749,7 +54084,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1043</v>
+        <v>1082</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -52769,7 +54104,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1044</v>
+        <v>1083</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">Y!E28</f>
